--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -64,6 +64,27 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1yAN_9f-mpcZudZCxnQSO8T9UYoAEpb8X</t>
+  </si>
+  <si>
+    <t>Humano, C.A.; Robles I. y V. Cruz</t>
+  </si>
+  <si>
+    <t>cahumano@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1VRTi0OW4pzcy7BF8uSfXUUm4uYk0oEFb</t>
+  </si>
+  <si>
+    <t>MODELADO DE PRECIOS MINORISTAS DE HORTALIZAS EN JUJUY: UN ENFOQUE BASADO EN MECANISMOS DE TRANSMISIÓN DE PRECIOS CON VECM</t>
+  </si>
+  <si>
+    <t>Solís, J. M.; León Ruiz, S. L.; Quespía Mamaní,, A.; Martínez, F. N.; Chaile, V. A.; Tolay Toconás, E. A.; Mercado, C. D.; Rosales, Y. B.; Chávez, J. L.; Yarbe, G. I.; Carrasco, S. C.; Leaño, M. C.</t>
+  </si>
+  <si>
+    <t>juanmasolis@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=18nA7Evgbs6QanNCLeKzq8HCCSagJ3OAQ</t>
   </si>
 </sst>
 </file>
@@ -73,7 +94,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -95,6 +116,11 @@
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -104,7 +130,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border/>
     <border>
       <left style="thin">
@@ -174,6 +200,34 @@
       </top>
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
       </bottom>
     </border>
     <border>
@@ -208,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -240,6 +294,15 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -300,7 +363,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G3" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G5" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -586,14 +649,56 @@
         <v>15</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5">
+        <v>45913.67557020833</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11">
+        <v>45913.97473407407</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F2"/>
     <hyperlink r:id="rId2" ref="F3"/>
+    <hyperlink r:id="rId3" ref="F4"/>
+    <hyperlink r:id="rId4" ref="F5"/>
   </hyperlinks>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId5"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -78,13 +78,34 @@
     <t>MODELADO DE PRECIOS MINORISTAS DE HORTALIZAS EN JUJUY: UN ENFOQUE BASADO EN MECANISMOS DE TRANSMISIÓN DE PRECIOS CON VECM</t>
   </si>
   <si>
-    <t>Solís, J. M.; León Ruiz, S. L.; Quespía Mamaní,, A.; Martínez, F. N.; Chaile, V. A.; Tolay Toconás, E. A.; Mercado, C. D.; Rosales, Y. B.; Chávez, J. L.; Yarbe, G. I.; Carrasco, S. C.; Leaño, M. C.</t>
+    <t>Solís, J. M.; León Ruiz, S. L.; Quespía Mamaní, A.; Martínez, F. N.; Chaile, V. A.; Tolay Toconás, E. A.; Mercado, C. D.; Rosales, Y. B.; Chávez, J. L.; Yarbe, G. I.; Carrasco, S. C.; Leaño, M. C.</t>
   </si>
   <si>
     <t>juanmasolis@fca.unju.edu.ar</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=18nA7Evgbs6QanNCLeKzq8HCCSagJ3OAQ</t>
+  </si>
+  <si>
+    <t>FACTORES QUE INFLUYEN EN LAS DIFICULTADES DE APRENDIZAJE EN QUÍMICA GENERAL: PERCEPCIONES DE ESTUDIANTES DE BROMATOLOGÍA</t>
+  </si>
+  <si>
+    <t>Rozo, V.; Burgos, C.; Cáceres, B.</t>
+  </si>
+  <si>
+    <t>valeriafernandarozo@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1HKugpS9Mjuy2OVabM8sR3CPBto3tg1bP</t>
+  </si>
+  <si>
+    <t>COMPOSICIÓN QUÍMICA DE ACEITES ESENCIALES DE ROMERO (Rosmarinus officinalis) Y TOMILLO (Thymus vulgaris). ESTUDIO DE SUS PROPIEDADES ANTIMICROBIANAS FRENTE A BACTERIAS GRAM NEGATIVAS</t>
+  </si>
+  <si>
+    <t>Rozo, V.; Huarachi, S. Zerpa, P; Sajama, G.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1EUAGIY8pYx5fZA2uH0Rj7kgYj0eTcdZD</t>
   </si>
 </sst>
 </file>
@@ -363,7 +384,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G5" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G7" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -670,23 +691,63 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11">
+      <c r="A5" s="8">
         <v>45913.97473407407</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="10" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5">
+        <v>45914.47360736111</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11">
+        <v>45914.475362847224</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -695,10 +756,12 @@
     <hyperlink r:id="rId2" ref="F3"/>
     <hyperlink r:id="rId3" ref="F4"/>
     <hyperlink r:id="rId4" ref="F5"/>
+    <hyperlink r:id="rId5" ref="F6"/>
+    <hyperlink r:id="rId6" ref="F7"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="61">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -106,6 +106,99 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1EUAGIY8pYx5fZA2uH0Rj7kgYj0eTcdZD</t>
+  </si>
+  <si>
+    <t>IMPLEMENTACIÓN DEL APRENDIZAJE BASADO EN PROYECTOS EN LAS ASIGNATURAS BIOESTADÍSTICA (LICENCIATURA EN CIENCIAS BIOLÓGICAS) Y ESTADÍSTICA (LICENCIATURA EN DESARROLLO RURAL) DE LA UNJU</t>
+  </si>
+  <si>
+    <t>Humacata, Ivone C.; Quiquinto, Amadeo J.: López, Alba V.; Leaño, Marta C. y Solís Juan M.</t>
+  </si>
+  <si>
+    <t>ivonehumacata@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=15qcb5iwmSjxMiiJL2wlPF_UPsTD3r_rB</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN MICROBIOLÓGICA DE LECHUGA (Lactuca sativa L.) PRODUCIDA EN HUERTAS ESCOLARES DEL DPTO. DR. MANUEL BELGRANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huarachi, SF.; Humacata, IC.; Arce, FB.; Balderrama, GC.; Sajama, G.; Zerpa, JP   </t>
+  </si>
+  <si>
+    <t>sergiohuarachi@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1b5cEYP4Im8mrCu5Kwc_-PTn8WCMXiAIb</t>
+  </si>
+  <si>
+    <t>HUERTA AGROECOLOGICA ESCOLAR: EL HUERTO DE COLORES</t>
+  </si>
+  <si>
+    <t>CESPEDES, S. CAIHURA,Z. CESPEDES, M. GASPAR, S. RUIZ, G Y BENITEZ AHRENDTS, H</t>
+  </si>
+  <si>
+    <t>silviacespedes@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1dggH6kFMzYeFFmX29Jil08LDrX4K1ogJ</t>
+  </si>
+  <si>
+    <t>ESTUDIOS PRELIMINARES SOBRE LA PRESENCIA DE BACTERIAS DEL GÉNERO Pseudomonas spp. EN RÍOS DE LA QUEBRADA DE HUMAHUACA, DURANTE ÉPOCA LLUVIOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huarachi, SF.; Alustiza, ME.; Madregal, SO.; Alfaro, JA.; Humacata, IC.; Moya, MN.; Alarcón E.; Contreras, ML. </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1RHGB2OosRE-HAdqoxklLM1XhnEE5r3BE</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN IN VIVO DE EXTRACTOS DE PROPÓLEOS FRENTE A NOSEMA SP. EN APIS MELLIFERA DE LA PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>Retamoso, R. M.; Benitez Ahrendts, M.R.</t>
+  </si>
+  <si>
+    <t>milagroretamoso@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qTJiKOAxBwJ8Lo-NwfG9ezubrI5nDmiX</t>
+  </si>
+  <si>
+    <t>CONTROL DE CALIDAD EN FRUTOS DE POMELO (Citrus paradisi): EVALUACIÓN DE LA CAPACIDAD DEL PROCESO EN PRECOSECHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singh, G. C.; Gimenez. L. A. S.; Quiquinto, A. J.; Catacata, J. R.; Agüero, A. A. </t>
+  </si>
+  <si>
+    <t>gcarolinasingh@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1P_eTFUsxCbx4urUD0X_7HXdtCdDSCz8k</t>
+  </si>
+  <si>
+    <t>EDUCACIÓN ALIMENTARIA EN LA FORMACIÓN DEL LICENCIADO EN BROMATOLOGÍA: EXPERIENCIAS DE CAPACITACIÓN EN CONTEXTOS REALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle, M. P. , López, A. G. </t>
+  </si>
+  <si>
+    <t>mariapaulacalle@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1RoVhZcw5X2DAK01YKFlN8td1suXsKI_A</t>
+  </si>
+  <si>
+    <t>REGULACIÓN ALIMENTARIA Y PERCEPCIONES EN FERIAS POPULARES DE JUJUY</t>
+  </si>
+  <si>
+    <t>López, A.G.; Calle, M.P.; Tolay, D.G.; Torres, M.A.</t>
+  </si>
+  <si>
+    <t>alejandralopez@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1fMvnGz8dsi0_veGh658qsaRR41Oy5_Lb</t>
   </si>
 </sst>
 </file>
@@ -384,7 +477,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G7" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G15" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -731,23 +824,183 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11">
+      <c r="A7" s="8">
         <v>45914.475362847224</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="10" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5">
+        <v>45914.665929930554</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8">
+        <v>45914.8153158912</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5">
+        <v>45914.82840233797</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8">
+        <v>45914.83085008102</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>45914.84970074074</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8">
+        <v>45914.88160112269</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>45914.883427685185</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11">
+        <v>45914.886963136574</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -758,10 +1011,18 @@
     <hyperlink r:id="rId4" ref="F5"/>
     <hyperlink r:id="rId5" ref="F6"/>
     <hyperlink r:id="rId6" ref="F7"/>
+    <hyperlink r:id="rId7" ref="F8"/>
+    <hyperlink r:id="rId8" ref="F9"/>
+    <hyperlink r:id="rId9" ref="F10"/>
+    <hyperlink r:id="rId10" ref="F11"/>
+    <hyperlink r:id="rId11" ref="F12"/>
+    <hyperlink r:id="rId12" ref="F13"/>
+    <hyperlink r:id="rId13" ref="F14"/>
+    <hyperlink r:id="rId14" ref="F15"/>
   </hyperlinks>
-  <drawing r:id="rId7"/>
+  <drawing r:id="rId15"/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -199,6 +199,57 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1fMvnGz8dsi0_veGh658qsaRR41Oy5_Lb</t>
+  </si>
+  <si>
+    <t>PERFIL PALINOLÓGICO Y NUTRICIONAL DEL POLEN APÍCOLA COSECHADO DURANTE LA CAMPAÑA 2024 -2025 EN SAN PEDRO JUJUY (ARGENTINA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Méndez, M.; Sánchez, A.; Flores, F.; Gallardo, S.; Rocha, L.;  Castro, F.; Batallanos, N.; Reynoso L.; Galeano Romero, E.; Lupo L. </t>
+  </si>
+  <si>
+    <t>magalivmendez@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1fKgFE_gIkK-pF3f_8D7AlV_3IvLt23Wu</t>
+  </si>
+  <si>
+    <t>USO DE ASERRÍN Y COMPOST COMO SUSTRATOS ALTERNATIVOS EN LA PRODUCCIÓN DE PLANTINES DE ENTEROLOBIUM CONTORTISILIQUUM “PACARA” EN LA PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>Geronimo, G.; Apaza, D.; Álvarez, M.; Herrera, D.; Atanasio, Y; Contreras M. y Vilca Ochoa, S.</t>
+  </si>
+  <si>
+    <t>miriangeronimo@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1SNnutaTtcCr0zvVHpmrJB95YLzb2Ee4I</t>
+  </si>
+  <si>
+    <t>TENDIENDO PUENTES ENTRE UNIVERSIDAD Y COMUNIDAD - PROYECTO “CRECE JUNTO A TU ÁRBOL”, VOLUNTARIADO UNIVERSITARIO</t>
+  </si>
+  <si>
+    <t>Geronimo, G.; Apaza, D.; Álvarez, M.; Herrera, D.; Guari, M.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ltJ15W4aJRmcUmom2zAnE2IGiM4_QQn5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Geronimo, G.; Apaza, D.; Álvarez, M.; Herrera, D.; Atanasio, Y.; Contreras M.; Vilca Ochoa, S.    </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=128FUaPWr_D7XUZf7L_yRd9eSd8aJTtw5</t>
+  </si>
+  <si>
+    <t>EL PODCAST Y LA RADIO EN VIVO COMO HERRAMIENTAS PEDAGÓGICAS PARA GESTIÓN AMBIENTAL</t>
+  </si>
+  <si>
+    <t>Civila Orellana, V; Alcade, A.S; Benicio, P.; Chavarría, D.</t>
+  </si>
+  <si>
+    <t>vanesacivila@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1nNhH4qpN_t9YgZolxseKLYDLM2BDCMc5</t>
   </si>
 </sst>
 </file>
@@ -349,10 +400,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -360,13 +411,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -477,7 +528,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G15" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G20" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -984,23 +1035,123 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11">
+      <c r="A15" s="8">
         <v>45914.886963136574</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="12" t="s">
+      <c r="B15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="10" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>45914.924989189814</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8">
+        <v>45914.962527905096</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>45914.96703664352</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8">
+        <v>45914.971597627315</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11">
+        <v>45914.97785438657</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1019,10 +1170,15 @@
     <hyperlink r:id="rId12" ref="F13"/>
     <hyperlink r:id="rId13" ref="F14"/>
     <hyperlink r:id="rId14" ref="F15"/>
+    <hyperlink r:id="rId15" ref="F16"/>
+    <hyperlink r:id="rId16" ref="F17"/>
+    <hyperlink r:id="rId17" ref="F18"/>
+    <hyperlink r:id="rId18" ref="F19"/>
+    <hyperlink r:id="rId19" ref="F20"/>
   </hyperlinks>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId20"/>
   <tableParts count="1">
-    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="82">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -250,6 +250,18 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1nNhH4qpN_t9YgZolxseKLYDLM2BDCMc5</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN DEL EFECTO CITOTOXICO DE MUÑA MUÑA (CLINOPODIUM GILLIESII) SOBRE GORGOJOS DEL POROTO (ACANTHOSCELIDES OBTECTUS)</t>
+  </si>
+  <si>
+    <t>Rivera Funes, M. C.; Cari, A. Y.; Leaño, M. C.</t>
+  </si>
+  <si>
+    <t>maria_riverafunes@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1swXoRRzkuQal3DEmI9v-BLFP_sQEd0nd</t>
   </si>
 </sst>
 </file>
@@ -400,10 +412,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -411,13 +423,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -528,7 +540,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G20" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G21" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1135,23 +1147,43 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11">
+      <c r="A20" s="5">
         <v>45914.97785438657</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="B20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="7" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11">
+        <v>45914.9960868287</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1175,10 +1207,11 @@
     <hyperlink r:id="rId17" ref="F18"/>
     <hyperlink r:id="rId18" ref="F19"/>
     <hyperlink r:id="rId19" ref="F20"/>
+    <hyperlink r:id="rId20" ref="F21"/>
   </hyperlinks>
-  <drawing r:id="rId20"/>
+  <drawing r:id="rId21"/>
   <tableParts count="1">
-    <tablePart r:id="rId22"/>
+    <tablePart r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -234,7 +234,7 @@
     <t>https://drive.google.com/open?id=1ltJ15W4aJRmcUmom2zAnE2IGiM4_QQn5</t>
   </si>
   <si>
-    <t xml:space="preserve"> Geronimo, G.; Apaza, D.; Álvarez, M.; Herrera, D.; Atanasio, Y.; Contreras M.; Vilca Ochoa, S.    </t>
+    <t xml:space="preserve">Geronimo, G.; Apaza, D.; Álvarez, M.; Herrera, D.; Atanasio, Y.; Contreras M.; Vilca Ochoa, S.    </t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=128FUaPWr_D7XUZf7L_yRd9eSd8aJTtw5</t>
@@ -262,6 +262,45 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1swXoRRzkuQal3DEmI9v-BLFP_sQEd0nd</t>
+  </si>
+  <si>
+    <t>HERRAMIENTAS PARA LA GESTIÓN SUSTENTABLE DEL ARBOLADO URBANO - METÁN, SALTA</t>
+  </si>
+  <si>
+    <t>Vargas, S. M. ; Vázquez, V. N.; Tapia, R.; Vargas, J. E.; Castillo Pérez, F.; Wilinsky, S.</t>
+  </si>
+  <si>
+    <t>svargas@sedesur.unsa.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1orFTh6IXkpXXcTmV-7YXqAP7TGLsHdhP</t>
+  </si>
+  <si>
+    <t>ESTUDIANTES (pasantía de trabajo final, tesina, horas de campo, práctica profesional, proyecto de investigación)</t>
+  </si>
+  <si>
+    <t>PROMOCIÓN DE PRÁCTICAS SUSTENTABLES EN SISTEMAS HORTÍCOLAS: EXTRACTOS VEGETALES CON CAPACIDAD BIOENRAIZANTE, BIOFERTILIZANTE Y BIOPROTECTORA</t>
+  </si>
+  <si>
+    <t>Flores, K.M.A.; López Mamani, J.M.; Ramos. A. J.; Castillo, A.V. ; Cruz, G.S. y  G .del C. Soto</t>
+  </si>
+  <si>
+    <t>gracielasoto@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1iUtQhbpTJi5SuY8vyt8DxgBoflY6U3y8</t>
+  </si>
+  <si>
+    <t>CARACTERIZACIÓN FISICOQUÍMICA DE PELÍCULAS COMESTIBLES A BASE DE ALMIDÓN DE PAPA Y ÁCIDO CÍTRICO COMO ADITIVO</t>
+  </si>
+  <si>
+    <t>Rojas, M. A.; Cruz, E. A.; Galarza, M. J.; Catacata, José R.3, Castro, Cristina N.</t>
+  </si>
+  <si>
+    <t>anamrojas@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1vckoyx9mN1pyy8tln6Y_HbXaWURezZrk</t>
   </si>
 </sst>
 </file>
@@ -412,10 +451,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -423,13 +462,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -540,7 +579,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G21" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G24" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1167,23 +1206,83 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11">
+      <c r="A21" s="8">
         <v>45914.9960868287</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="12" t="s">
+      <c r="B21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="10" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>45915.02726991898</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8">
+        <v>45915.060963020835</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11">
+        <v>45915.35040892361</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1208,10 +1307,13 @@
     <hyperlink r:id="rId18" ref="F19"/>
     <hyperlink r:id="rId19" ref="F20"/>
     <hyperlink r:id="rId20" ref="F21"/>
+    <hyperlink r:id="rId21" ref="F22"/>
+    <hyperlink r:id="rId22" ref="F23"/>
+    <hyperlink r:id="rId23" ref="F24"/>
   </hyperlinks>
-  <drawing r:id="rId21"/>
+  <drawing r:id="rId24"/>
   <tableParts count="1">
-    <tablePart r:id="rId23"/>
+    <tablePart r:id="rId26"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="96">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1vckoyx9mN1pyy8tln6Y_HbXaWURezZrk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=19_5xcIYDZW9gfPhAsRKD5kDm05lTH46o</t>
   </si>
 </sst>
 </file>
@@ -451,10 +454,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -462,13 +465,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -579,7 +582,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G24" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G25" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1266,23 +1269,43 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11">
+      <c r="A24" s="5">
         <v>45915.35040892361</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="12" t="s">
+      <c r="B24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="7" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11">
+        <v>45915.534532997684</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1310,10 +1333,11 @@
     <hyperlink r:id="rId21" ref="F22"/>
     <hyperlink r:id="rId22" ref="F23"/>
     <hyperlink r:id="rId23" ref="F24"/>
+    <hyperlink r:id="rId24" ref="F25"/>
   </hyperlinks>
-  <drawing r:id="rId24"/>
+  <drawing r:id="rId25"/>
   <tableParts count="1">
-    <tablePart r:id="rId26"/>
+    <tablePart r:id="rId27"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="107">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -304,6 +304,39 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=19_5xcIYDZW9gfPhAsRKD5kDm05lTH46o</t>
+  </si>
+  <si>
+    <t>ESPOROFITOS DE DOS ESPECIES DEL COMPLEJO ASPLENIUM SERRA (ASPLENIACEAE) DE LAS YUNGAS ARGENTINAS, MEDIANTE LA APLICACION DE TECNICAS DE LABORATORIO CONVENCIONALES.</t>
+  </si>
+  <si>
+    <t>Prats, F. M.; Ganem, M. A.</t>
+  </si>
+  <si>
+    <t>florenciamprats@gmail.com</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=11IEyQTkmK9ypRRcDWYAk66J7COlsmUZ7</t>
+  </si>
+  <si>
+    <t>Flores, K.M.A.; López Mamani, J.M.; Ramos. A. J.; Castillo, A.V.; Cruz, G.S. y Soto, G .del C.</t>
+  </si>
+  <si>
+    <t>Ayelenflores606@gmail.com</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1oijHVPpVQo6iicFIkyvhzOO7ZGD1Auuc</t>
+  </si>
+  <si>
+    <t>FACTORES QUE INCIDEN EN LA DESERCIÓN Y REPROBACIÓN DE LOS ESTUDIANTES EN LA MATERIA DE ÁLGEBRA Y GEOMETRÍA ANALÍTICA EN LA FACULTAD DE CIENCIAS AGRARIAS.</t>
+  </si>
+  <si>
+    <t>López, I.; Guanuco A.; Saravia, I.; Bautista, J.; Aguado, R. Calizaya, B.; Cruz, A.</t>
+  </si>
+  <si>
+    <t>indiramacarenalopez@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1SmJTqJQYZryQRvrIvD8VJCQtV5otNWAn</t>
   </si>
 </sst>
 </file>
@@ -454,10 +487,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -465,13 +498,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -582,7 +615,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G25" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G28" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1289,23 +1322,83 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11">
+      <c r="A25" s="8">
         <v>45915.534532997684</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="12" t="s">
+      <c r="B25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="10" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5">
+        <v>45915.65178042824</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8">
+        <v>45915.67254356481</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11">
+        <v>45915.692211747686</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1334,10 +1427,13 @@
     <hyperlink r:id="rId22" ref="F23"/>
     <hyperlink r:id="rId23" ref="F24"/>
     <hyperlink r:id="rId24" ref="F25"/>
+    <hyperlink r:id="rId25" ref="F26"/>
+    <hyperlink r:id="rId26" ref="F27"/>
+    <hyperlink r:id="rId27" ref="F28"/>
   </hyperlinks>
-  <drawing r:id="rId25"/>
+  <drawing r:id="rId28"/>
   <tableParts count="1">
-    <tablePart r:id="rId27"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="117">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -337,6 +337,36 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1SmJTqJQYZryQRvrIvD8VJCQtV5otNWAn</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN DE PRÁCTICAS DEL USO DE SAL Y CONOCIMIENTOS EN PANADERÍAS DE LA PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>Barco, A.; Guanuco, M.; Alfaro, J.; González, Y.; Velázquez P.; Maizares , A; Espinosa, C.; Cruz, M., Nuñez Souza, M.; Alfaro, M. y Rueda, J.</t>
+  </si>
+  <si>
+    <t>adriabarco26@gmail.com</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=13i9UKtoZj7QZb9MhyCy5hMvrN237DWA4</t>
+  </si>
+  <si>
+    <t>Flores, K.M.A.;, López Mamani, J.M.; Ramos. A. J. ; Castillo, A.V.; Cruz, G.S. y G. del C., Soto</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1nTzvkePiRhgUlw-xMrAA0fkH5_ICeM96</t>
+  </si>
+  <si>
+    <t>MAPA DE FERTILIDAD CON USO DE VARIABLES FÍSICAS-QUÍMICAS DEL SUELO DEL CAMPO EXPERIMENTAL DR. EMILIO NAVEA, FCA-UNJu</t>
+  </si>
+  <si>
+    <t>Aprile, G. J.; Martinez, L.; Arias, P. M.; Solis, J.</t>
+  </si>
+  <si>
+    <t>gastonaprile@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1HQLviHiXKGN88v3t8g6rx8uI73OxbTIp</t>
   </si>
 </sst>
 </file>
@@ -487,10 +517,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -498,13 +528,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -615,7 +645,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G28" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G31" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1382,23 +1412,83 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11">
+      <c r="A28" s="5">
         <v>45915.692211747686</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="12" t="s">
+      <c r="B28" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="7" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8">
+        <v>45915.788852592596</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5">
+        <v>45915.93563230324</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11">
+        <v>45915.939361550925</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1430,10 +1520,13 @@
     <hyperlink r:id="rId25" ref="F26"/>
     <hyperlink r:id="rId26" ref="F27"/>
     <hyperlink r:id="rId27" ref="F28"/>
+    <hyperlink r:id="rId28" ref="F29"/>
+    <hyperlink r:id="rId29" ref="F30"/>
+    <hyperlink r:id="rId30" ref="F31"/>
   </hyperlinks>
-  <drawing r:id="rId28"/>
+  <drawing r:id="rId31"/>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId33"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="118">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -360,13 +360,16 @@
     <t>MAPA DE FERTILIDAD CON USO DE VARIABLES FÍSICAS-QUÍMICAS DEL SUELO DEL CAMPO EXPERIMENTAL DR. EMILIO NAVEA, FCA-UNJu</t>
   </si>
   <si>
-    <t>Aprile, G. J.; Martinez, L.; Arias, P. M.; Solis, J.</t>
+    <t>Aprile, G. J.; Vera, R.; Martinez, L.; Arias, P. M.; Solis, J.</t>
   </si>
   <si>
     <t>gastonaprile@fca.unju.edu.ar</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1HQLviHiXKGN88v3t8g6rx8uI73OxbTIp</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ZSQLVC4dbaqg4ychLbjoqHVyIpsL-TbM</t>
   </si>
 </sst>
 </file>
@@ -376,7 +379,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -387,6 +390,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <u/>
@@ -517,10 +525,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -528,13 +536,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -544,7 +552,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -578,13 +586,16 @@
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -645,7 +656,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G31" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G32" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1472,23 +1483,43 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11">
+      <c r="A31" s="8">
         <v>45915.939361550925</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="11" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12">
+        <v>45915.98990030093</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1523,10 +1554,11 @@
     <hyperlink r:id="rId28" ref="F29"/>
     <hyperlink r:id="rId29" ref="F30"/>
     <hyperlink r:id="rId30" ref="F31"/>
+    <hyperlink r:id="rId31" ref="F32"/>
   </hyperlinks>
-  <drawing r:id="rId31"/>
+  <drawing r:id="rId32"/>
   <tableParts count="1">
-    <tablePart r:id="rId33"/>
+    <tablePart r:id="rId34"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="126">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -45,7 +45,7 @@
     <t>ESTIMACIÓN DE ÍNDICES DE PRECIOS MAYORISTAS DE LAS PRINCIPALES FRUTAS Y HORTALIZAS RELEVADAS EN EL MERCADO FORMADOR DE PRECIOS DE LA REGIÓN DEL NOA ARGENTINO</t>
   </si>
   <si>
-    <t>Riba, G.; Lipchak, V.A.; Velasquez, P.V.; Arjona, C.</t>
+    <t>Riba, G.; Solís, J.; Lipchak, V.A.; Velasquez, P.V.; Arjona, C.</t>
   </si>
   <si>
     <t>gastonriba@fca.unju.edu.ar</t>
@@ -370,6 +370,30 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1ZSQLVC4dbaqg4ychLbjoqHVyIpsL-TbM</t>
+  </si>
+  <si>
+    <t>MANITAS LIMPIAS SALVAN VIDAS</t>
+  </si>
+  <si>
+    <t>Catacata, A.; Rodriguez,C.I.</t>
+  </si>
+  <si>
+    <t>analiacatacata@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ofjueuOTLta4a_scththhoUoZYPZttzC</t>
+  </si>
+  <si>
+    <t>CARACTERIZACIÓN MORFOLÓGICA Y FÍSICA DE ACCESIONES CRIOLLAS DE HABAS (VICIA FABA L.)</t>
+  </si>
+  <si>
+    <t>Paredes, C.M.; Lopez Mamani, M.J; Cabezas, J; Britos, J.</t>
+  </si>
+  <si>
+    <t>claudiaparedes@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1qGIdPVNW9a_U0NVpnTmnlZwCjbZOH9gJ</t>
   </si>
 </sst>
 </file>
@@ -656,7 +680,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G32" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G34" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1503,23 +1527,63 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12">
+      <c r="A32" s="5">
         <v>45915.98990030093</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="7" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8">
+        <v>45916.29016259259</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12">
+        <v>45916.30174447916</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1555,10 +1619,12 @@
     <hyperlink r:id="rId29" ref="F30"/>
     <hyperlink r:id="rId30" ref="F31"/>
     <hyperlink r:id="rId31" ref="F32"/>
+    <hyperlink r:id="rId32" ref="F33"/>
+    <hyperlink r:id="rId33" ref="F34"/>
   </hyperlinks>
-  <drawing r:id="rId32"/>
+  <drawing r:id="rId34"/>
   <tableParts count="1">
-    <tablePart r:id="rId34"/>
+    <tablePart r:id="rId36"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="128">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -394,6 +394,12 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1qGIdPVNW9a_U0NVpnTmnlZwCjbZOH9gJ</t>
+  </si>
+  <si>
+    <t>Humacata, Ivone C.; Quiquinto, Amadeo J.;  López, Alba V.; Leaño, Marta C. y Solís, Juan M.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1e8_k5qKiJxBl26WlVJMOum3TKJKhQXOO</t>
   </si>
 </sst>
 </file>
@@ -549,10 +555,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -560,13 +566,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -680,7 +686,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G34" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G35" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1567,23 +1573,43 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12">
+      <c r="A34" s="5">
         <v>45916.30174447916</v>
       </c>
-      <c r="B34" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="13" t="s">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="7" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12">
+        <v>45917.38095521991</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1621,10 +1647,11 @@
     <hyperlink r:id="rId31" ref="F32"/>
     <hyperlink r:id="rId32" ref="F33"/>
     <hyperlink r:id="rId33" ref="F34"/>
+    <hyperlink r:id="rId34" ref="F35"/>
   </hyperlinks>
-  <drawing r:id="rId34"/>
+  <drawing r:id="rId35"/>
   <tableParts count="1">
-    <tablePart r:id="rId36"/>
+    <tablePart r:id="rId37"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="132">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -400,6 +400,18 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1e8_k5qKiJxBl26WlVJMOum3TKJKhQXOO</t>
+  </si>
+  <si>
+    <t>ICTIOFAUNA DEL RÍO XIBI-XIBI (JUJUY): UNA APROXIMACIÓN AL CONOCIMIENTO DE SU DIVERSIDAD Y DISTRIBUCIÓN</t>
+  </si>
+  <si>
+    <t>Quispe, J.; Vargas Rodríguez, N.</t>
+  </si>
+  <si>
+    <t>ferhandball562@gmail.com</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1s4gReRvPVcp1sfLPVN6gbubNCz5f3Fwh</t>
   </si>
 </sst>
 </file>
@@ -555,10 +567,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -566,13 +578,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -686,7 +698,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G35" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G36" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1593,23 +1605,43 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12">
+      <c r="A35" s="8">
         <v>45917.38095521991</v>
       </c>
-      <c r="B35" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="13" t="s">
+      <c r="B35" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="10" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12">
+        <v>45917.787255567135</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1648,10 +1680,11 @@
     <hyperlink r:id="rId32" ref="F33"/>
     <hyperlink r:id="rId33" ref="F34"/>
     <hyperlink r:id="rId34" ref="F35"/>
+    <hyperlink r:id="rId35" ref="F36"/>
   </hyperlinks>
-  <drawing r:id="rId35"/>
+  <drawing r:id="rId36"/>
   <tableParts count="1">
-    <tablePart r:id="rId37"/>
+    <tablePart r:id="rId38"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="139">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -412,6 +412,27 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1s4gReRvPVcp1sfLPVN6gbubNCz5f3Fwh</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN DE DIFERENTES INDICADORES DE CALIDAD DE GRANO EN UN GENOTIPO DE SOJA (GLYCINE MAX (L) CULTIVADO EN AMBIENTES CONTRASTANTES</t>
+  </si>
+  <si>
+    <t>Manero, J.; Almazán, L.; Mendoza, J.; Chali, S.; Miranda, R.; Amaya, A.; Acosta, J.</t>
+  </si>
+  <si>
+    <t>fedemanero@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1xwRXtOl1HBsRUP4Ne-rEkE6s1suNI2a_</t>
+  </si>
+  <si>
+    <t>PRÁCTICAS AGROECOLÓGICAS DE CONTROL SANITARIO EN EL CULTIVO DE PAPA (SOLANUM TUBEROSUM VAR. SPUNTA) EN LA ESCUELA PROVINCIAL AGROTECNCIA N°1 EL BRETE-PALPALA</t>
+  </si>
+  <si>
+    <t>CESPEDES, S., CAIHUARA, H.,BENITEZ AHRENDTS,H., VILCA, E.M</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=10G-fqiXG0gLGZqquxlg6o2s7X4Ku2Axh</t>
   </si>
 </sst>
 </file>
@@ -698,7 +719,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G36" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G38" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1625,23 +1646,63 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12">
+      <c r="A36" s="5">
         <v>45917.787255567135</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="7" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8">
+        <v>45919.40681840278</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12">
+        <v>45921.69627556713</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1681,10 +1742,12 @@
     <hyperlink r:id="rId33" ref="F34"/>
     <hyperlink r:id="rId34" ref="F35"/>
     <hyperlink r:id="rId35" ref="F36"/>
+    <hyperlink r:id="rId36" ref="F37"/>
+    <hyperlink r:id="rId37" ref="F38"/>
   </hyperlinks>
-  <drawing r:id="rId36"/>
+  <drawing r:id="rId38"/>
   <tableParts count="1">
-    <tablePart r:id="rId38"/>
+    <tablePart r:id="rId40"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="143">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -433,6 +433,18 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=10G-fqiXG0gLGZqquxlg6o2s7X4Ku2Axh</t>
+  </si>
+  <si>
+    <t>ESTUDIO DE PARÁMETROS REPRODUCTIVOS EN OVINOS CON VISTAS AL MEJORAMIENTO GENÉTICO EN LA ECOREGIÓN PUNA. PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>Guari, C. G.; Abalos M. C.;  Castro Y. M.</t>
+  </si>
+  <si>
+    <t>yaninacastro@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1OqNOEEWqdk1CE_rZT1S5ERMZPJOuwpk_</t>
   </si>
 </sst>
 </file>
@@ -588,10 +600,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -599,13 +611,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -719,7 +731,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G38" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G39" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1686,23 +1698,43 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12">
+      <c r="A38" s="5">
         <v>45921.69627556713</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="13" t="s">
+      <c r="B38" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="7" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12">
+        <v>45922.03633664352</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1744,10 +1776,11 @@
     <hyperlink r:id="rId35" ref="F36"/>
     <hyperlink r:id="rId36" ref="F37"/>
     <hyperlink r:id="rId37" ref="F38"/>
+    <hyperlink r:id="rId38" ref="F39"/>
   </hyperlinks>
-  <drawing r:id="rId38"/>
+  <drawing r:id="rId39"/>
   <tableParts count="1">
-    <tablePart r:id="rId40"/>
+    <tablePart r:id="rId41"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="149">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -445,6 +445,24 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1OqNOEEWqdk1CE_rZT1S5ERMZPJOuwpk_</t>
+  </si>
+  <si>
+    <t>Manero, J.; Almazan, L.; Mendoza, J.; Chañi, S.; Miranda, R.; Amaya, A.; Acosta, J.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=15y_X5RqKXeJnJi3gTzXYdtNOn2l9suoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manero, J.; Almazán, L.; Mendoza, J.; Chañi, S.; Miranda, R.; Amaya, A.; Acosta, J.M. </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1D_UHiR_A7Q7E3EGQjA8TI3n_bzXz5wYW</t>
+  </si>
+  <si>
+    <t>Manero, F.; Almazán, L.; Mendoza, J.; Chañi, S.; Miranda, M.; Amaya, A.; Acosta, J.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1aTnRLJQ8vp5GcOLnSLh_QjQdO_rvmcut</t>
   </si>
 </sst>
 </file>
@@ -600,10 +618,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -611,13 +629,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -731,7 +749,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G39" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G42" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1718,23 +1736,83 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12">
+      <c r="A39" s="8">
         <v>45922.03633664352</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="10" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5">
+        <v>45922.5880340625</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8">
+        <v>45922.64668114584</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12">
+        <v>45922.71198054398</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1777,10 +1855,13 @@
     <hyperlink r:id="rId36" ref="F37"/>
     <hyperlink r:id="rId37" ref="F38"/>
     <hyperlink r:id="rId38" ref="F39"/>
+    <hyperlink r:id="rId39" ref="F40"/>
+    <hyperlink r:id="rId40" ref="F41"/>
+    <hyperlink r:id="rId41" ref="F42"/>
   </hyperlinks>
-  <drawing r:id="rId39"/>
+  <drawing r:id="rId42"/>
   <tableParts count="1">
-    <tablePart r:id="rId41"/>
+    <tablePart r:id="rId44"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="157">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -463,6 +463,30 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1aTnRLJQ8vp5GcOLnSLh_QjQdO_rvmcut</t>
+  </si>
+  <si>
+    <t>CONTROL DE CALIDAD FÍSICO-QUÍMICA EN VINOS ELABORADOS EN UNA BODEGA BOUTIQUE DE LA PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>Balderrama, G; Vacaflor, G; Castillo, C; Choque, D</t>
+  </si>
+  <si>
+    <t>choquedaniela@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1FiFlgIJVTMj8ToRvUEEq4NGfJlrsDSkq</t>
+  </si>
+  <si>
+    <t>DIVERSIDAD ENDOFÍTICA DE TECOMA STANS (GUARÁN-GUARÁN) EN JUJUY</t>
+  </si>
+  <si>
+    <t>Segovia, A.; Giulianotti, C.; Catacata, J.</t>
+  </si>
+  <si>
+    <t>nelitas49@gmail.com</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1XM0YtQRaGYE5Aig6t15Lspkbp4DrMaaL</t>
   </si>
 </sst>
 </file>
@@ -749,7 +773,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G42" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G44" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1796,23 +1820,63 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12">
+      <c r="A42" s="5">
         <v>45922.71198054398</v>
       </c>
-      <c r="B42" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="13" t="s">
+      <c r="B42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="7" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8">
+        <v>45923.01586659723</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12">
+        <v>45923.4055628125</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1858,10 +1922,12 @@
     <hyperlink r:id="rId39" ref="F40"/>
     <hyperlink r:id="rId40" ref="F41"/>
     <hyperlink r:id="rId41" ref="F42"/>
+    <hyperlink r:id="rId42" ref="F43"/>
+    <hyperlink r:id="rId43" ref="F44"/>
   </hyperlinks>
-  <drawing r:id="rId42"/>
+  <drawing r:id="rId44"/>
   <tableParts count="1">
-    <tablePart r:id="rId44"/>
+    <tablePart r:id="rId46"/>
   </tableParts>
 </worksheet>
 </file>
--- a/FORMULARIO/DATOS.xlsx
+++ b/FORMULARIO/DATOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="161">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -487,6 +487,18 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1XM0YtQRaGYE5Aig6t15Lspkbp4DrMaaL</t>
+  </si>
+  <si>
+    <t>COMPARACIÓN DE ÍNDICES DE SEQUÍA BASADOS EN LA PRECIPITACIÓN PARA LA PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>Moreno, C.; Rivera Funes, M.; Valdiviezo Corte, M.; Vilca Ochoa, S.</t>
+  </si>
+  <si>
+    <t>carlamoreno@fca.unju.edu.ar</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=18-v0fBaLSFsquaF2fS61ZCM4KABY5VCf</t>
   </si>
 </sst>
 </file>
@@ -642,10 +654,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -653,13 +665,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -773,7 +785,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G44" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G45" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="7">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="CATEGORÍA_x000a_(En caso de varias categorías, seleccionar la del primer autor)" id="2"/>
@@ -1860,23 +1872,43 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12">
+      <c r="A44" s="5">
         <v>45923.4055628125</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="7" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12">
+        <v>45924.50855210648</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1924,10 +1956,11 @@
     <hyperlink r:id="rId41" ref="F42"/>
     <hyperlink r:id="rId42" ref="F43"/>
     <hyperlink r:id="rId43" ref="F44"/>
+    <hyperlink r:id="rId44" ref="F45"/>
   </hyperlinks>
-  <drawing r:id="rId44"/>
+  <drawing r:id="rId45"/>
   <tableParts count="1">
-    <tablePart r:id="rId46"/>
+    <tablePart r:id="rId47"/>
   </tableParts>
 </worksheet>
 </file>